--- a/mosip_master/xlsx/ui_spec.xlsx
+++ b/mosip_master/xlsx/ui_spec.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\eclipse-workspace\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04C5009-E5DA-4645-B9D9-41C0591431D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122FA483-88F6-41FA-9785-58BD02270426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
   <si>
     <t>id</t>
   </si>
@@ -130,12 +130,6 @@
     <t>updateProcess</t>
   </si>
   <si>
-    <t>lostProcess</t>
-  </si>
-  <si>
-    <t>bioCorrectionProcess</t>
-  </si>
-  <si>
     <t>cd005fa3-49bd-4de4-8634-81372b707fd1</t>
   </si>
   <si>
@@ -155,18 +149,6 @@
   </si>
   <si>
     <t>Update Registration process</t>
-  </si>
-  <si>
-    <t>78f07cba-0f5d-4e28-a970-f85d1ac302c9</t>
-  </si>
-  <si>
-    <t>Lost Registration process</t>
-  </si>
-  <si>
-    <t>6a080562-86d0-4dba-8bd9-4bdc89243e70</t>
-  </si>
-  <si>
-    <t>Biometric correction Registration process</t>
   </si>
   <si>
     <t>Pre-registration UI Specification</t>
@@ -488,2399 +470,6 @@
 		]
 	}
 ]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
-  "id": "UPDATE",
-  "order": 2,
-  "flow": "UPDATE",
-  "label": {
-    "eng": "Update UIN",
-    "por": "Atualizar UIN"
-  },
-  "screens": [
-    {
-      "order": 1,
-      "name": "consentdet",
-      "label": {
-        "eng": "Consent",
-        "por": "Consentimento"
-      },
-      "caption": {
-        "eng": "Consent",
-        "por": "Consentimento"
-      },
-      "fields": [
-        {
-          "id": "consentText",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Consent",
-          "label": {},
-          "controlType": "html",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "evidence",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "Consent",
-          "groupLabel": {
-            "eng": "Consent",
-            "por": "Consentimento"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": "Registration Consent",
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "consentText",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "consent",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "consent accepted",
-          "label": {
-            "eng": "I have read and accept terms and conditions to share my PII",
-            "por": "Li e aceito os termos e condições para compartilhar minhas informações pessoais."
-          },
-          "controlType": "checkbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "evidence",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "Consent",
-          "groupLabel": {
-            "ara": "موافقة",
-            "fra": "Consentement",
-            "eng": "Consent",
-            "por": "Consentimento"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "consent",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "preferredLang",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "user preferred Language",
-          "label": {
-            "eng": "Notification Langauge",
-            "por": "Idioma de notificação"
-          },
-          "controlType": "button",
-          "fieldType": "dynamic",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "group1",
-          "visible": null,
-          "contactType": null,
-          "group": "PreferredLanguage",
-          "groupLabel": {
-            "eng": "Notification Langauge",
-            "por": "Idioma de notificação"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "preferredLang",
-          "exceptionPhotoRequired": false
-        }
-      ],
-      "layoutTemplate": null,
-      "preRegFetchRequired": false,
-      "additionalInfoRequestIdRequired": false,
-      "active": false
-    },
-    {
-      "order": 2,
-      "name": "DemographicDetails",
-      "label": {
-        "eng": "Demographic Details",
-        "por": "Detalhes demográficos"
-      },
-      "caption": {
-        "eng": "Demographic Details",
-        "por": "Detalhes demográficos"
-      },
-      "fields": [
-        {
-          "id": "firstName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "First Name",
-          "label": {
-            "eng": "First Name",
-            "por": "Primeiro nome"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "FullName",
-          "groupLabel": {
-            "eng": "Full Name",
-            "por": "Nome completo"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "firstName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "surname",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Surname",
-          "label": {
-            "eng": "Surname",
-            "por": "Sobrenome"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "FullName",
-          "groupLabel": {
-            "eng": "Full Name",
-            "por": "Nome completo"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "surname",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "dateOfBirth",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "dateOfBirth",
-          "label": {
-            "eng": "Date of Birth",
-            "por": "Data de nascimento"
-          },
-          "controlType": "ageDate",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "DateOfBirth",
-          "groupLabel": {
-            "eng": "Date of Birth",
-            "por": "Data de nascimento"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "dateOfBirth",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "gender",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "gender",
-          "label": {
-            "eng": "Gender",
-            "por": "Gênero"
-          },
-          "controlType": "button",
-          "fieldType": "dynamic",
-          "format": "",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "group1",
-          "visible": null,
-          "contactType": null,
-          "group": "Gender",
-          "groupLabel": {
-            "eng": "Gender",
-            "por": "Gênero"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "gender",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "height",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Height",
-          "label": {
-            "eng": "Height (cm)",
-            "por": "Altura (cm)"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^[0-9]{1,3}$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "PhysicalDetails",
-          "groupLabel": {
-            "eng": "Physical Details",
-            "por": "Detalhes físicos"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "height",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "residenceStatus",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "residenceStatus",
-          "label": {
-            "eng": "Residence Status",
-            "por": "Status de residência"
-          },
-          "controlType": "button",
-          "fieldType": "dynamic",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "kyc",
-          "alignmentGroup": "group1",
-          "visible": null,
-          "contactType": null,
-          "group": "ResidenceStatus",
-          "groupLabel": {
-            "eng": "Residence Status",
-            "por": "Status de residência"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "residenceStatus",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "countryOfCitizenship",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Country of Citizenship",
-          "label": {
-            "eng": "Country of Citizenship",
-            "por": "País de cidadania"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": null,
-          "group": "CountryOfCitizenship",
-          "groupLabel": {
-            "eng": "Country of Citizenship",
-            "por": "País de cidadania"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "countryOfCitizenship",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "maritalStatus",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Marital Status",
-          "label": {
-            "eng": "Marital Status",
-            "por": "Estado civil"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "MaritalStatus",
-          "groupLabel": {
-            "eng": "Marital Status",
-            "por": "Estado civil"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "maritalStatus",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "fatherName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Father's Name",
-          "label": {
-            "eng": "Father's Name",
-            "por": "Nome do pai"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "ParentsDetails",
-          "groupLabel": {
-            "eng": "Parents Details",
-            "por": "Detalhes dos pais"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "fatherName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "motherName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Mother's Name",
-          "label": {
-            "eng": "Mother's Name",
-            "por": "Nome da mãe"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "ParentsDetails",
-          "groupLabel": {
-            "eng": "Parents Details",
-            "por": "Detalhes dos pais"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "motherName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "addressLine1",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "addressLine1",
-          "label": {
-            "eng": "Address Line 1",
-            "por": "Endereço, linha 1"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{0,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "address",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Address",
-          "groupLabel": {
-            "eng": "Address",
-            "por": "Endereço"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "addressLine1",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "addressLine2",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "addressLine2",
-          "label": {
-            "eng": "Address Line 2",
-            "por": "Endereço, linha 2"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{3,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "address",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Address",
-          "groupLabel": {
-            "eng": "Address",
-            "por": "Endereço"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "addressLine2",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "island",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Island",
-          "label": {
-            "eng": "Island",
-            "por": "Ilha"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": {
-            "eng": "Local Location",
-            "por": "Localização local"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Ilhas",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "district",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "District",
-          "label": {
-            "eng": "District",
-            "por": "Distrito"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": {
-            "eng": "Local Location",
-            "por": "Localização local"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Distrito",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "town",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Town",
-          "label": {
-            "eng": "Town",
-            "por": "Cidade"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": {
-            "eng": "Local Location",
-            "por": "Localização local"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Cidade",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "municipality",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Municipality",
-          "label": {
-            "eng": "Municipality",
-            "por": "Município"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": {
-            "eng": "Local Location",
-            "por": "Localização local"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Município",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "mobileNumber",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Mobile Number",
-          "label": {
-            "eng": "Mobile Number",
-            "por": "Número de celular"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^\\+239\\s?[0-9]{7}$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "contact",
-          "visible": null,
-          "contactType": "Phone",
-          "group": "Phone",
-          "groupLabel": {
-            "eng": "Phone",
-            "por": "Telefone"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "MobileNumber",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "email",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "email",
-          "label": {
-            "eng": "Email",
-            "por": "E-mail"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "contact",
-          "visible": null,
-          "contactType": "email",
-          "group": "Email",
-          "groupLabel": {
-            "eng": "Email",
-            "por": "E-mail"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Email",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "introducerName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Legal Guardian Name",
-          "label": {
-            "eng": "Legal Guardian Name",
-            "por": "Nome do responsável legal"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "evidence",
-          "alignmentGroup": "introducer",
-          "visible": null,
-          "contactType": null,
-          "group": "IntroducerDetails",
-          "groupLabel": {
-            "eng": "Legal Guardian Details",
-            "por": "Detalhes do responsável legal"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "introducerName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "introducerRID",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Legal Guardian RID",
-          "label": {
-            "eng": "Legal Guardian RID",
-            "por": "RID do responsável legal"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^([0-9]{10,30})$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "evidence",
-          "alignmentGroup": "introducer",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty"
-          },
-          "contactType": null,
-          "group": "IntroducerDetails",
-          "groupLabel": {
-            "eng": "Legal Guardian Details",
-            "por": "Detalhes do responsável legal"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty"
-            }
-          ],
-          "subType": "RID",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "introducerUIN",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Legal Guardian UIN",
-          "label": {
-            "eng": "Legal Guardian UIN",
-            "por": "UIN do responsável legal"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^([0-9]{10,30})$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "evidence",
-          "alignmentGroup": "introducer",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "identity.get('introducerRID') == nil || identity.get('introducerRID') == empty"
-          },
-          "contactType": null,
-          "group": "IntroducerDetails",
-          "groupLabel": {
-            "eng": "Legal Guardian Details",
-            "por": "Detalhes do responsável legal"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "identity.get('introducerRID') == nil || identity.get('introducerRID') == empty"
-            }
-          ],
-          "subType": "UIN",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "passportNumber",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Passport Number",
-          "label": {
-            "eng": "Passport Number",
-            "por": "Número do passaporte"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "kyc",
-          "alignmentGroup": null,
-          "visible": {
-            "engine": "MVEL",
-            "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-          },
-          "contactType": null,
-          "group": "PassportDetails",
-          "groupLabel": {
-            "eng": "Passport Details",
-            "por": "Detalhes do passaporte"
-          },
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-            }
-          ],
-          "subType": "passportNumber",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "passportIssuingCountry",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Passport Issuing Country",
-          "label": {
-            "eng": "Issuing Country",
-            "por": "País emissor"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "kyc",
-          "alignmentGroup": "location",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-          },
-          "contactType": null,
-          "group": "PassportDetails",
-          "groupLabel": {
-            "eng": "Passport </t>
-  </si>
-  <si>
-    <t xml:space="preserve">{
-  "id": "LOST",
-  "order": 3,
-  "flow": "LOST",
-  "label": {
-    "eng": "Lost UIN",
-    "por": "Perdido UIN"
-  },
-  "screens": [
-    {
-      "order": 1,
-      "name": "consentdet",
-      "label": {
-        "eng": "Consent",
-        "por": "Consentimento"
-      },
-      "caption": {
-        "eng": "Consent",
-        "por": "Consentimento"
-      },
-      "fields": [
-        {
-          "id": "IDSchemaVersion",
-          "inputRequired": false,
-          "type": "number",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "ID Schema Version",
-          "label": {
-            "eng": "IDSchemaVersion"
-          },
-          "controlType": null,
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "none",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": null,
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "IdSchemaVersion",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "consentText",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Consent",
-          "label": {},
-          "controlType": "html",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "evidence",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "consentText",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": "Registration Consent",
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "consentText",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "consent",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "consent accepted",
-          "label": {
-            "eng": "I have read and accept terms and conditions to share my PII",
-            "por": "Li e aceito os termos e condições para compartilhar minhas informações pessoais."
-          },
-          "controlType": "checkbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "evidence",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "consent",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "consent",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "preferredLang",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "user preferred Language",
-          "label": {
-            "eng": "Notification Langauge",
-            "por": "Idioma de notificação"
-          },
-          "controlType": "button",
-          "fieldType": "dynamic",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "group1",
-          "visible": null,
-          "contactType": null,
-          "group": "PreferredLanguage",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": true,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "preferredLang",
-          "exceptionPhotoRequired": false
-        }
-      ],
-      "layoutTemplate": null,
-      "preRegFetchRequired": false,
-      "additionalInfoRequestIdRequired": false,
-      "active": false
-    },
-    {
-      "order": 2,
-      "name": "DemographicDetails",
-      "label": {
-        "eng": "Demographic Details",
-        "por": "Detalhes demográficos"
-      },
-      "caption": {
-        "eng": "Demographic Details",
-        "por": "Detalhes demográficos"
-      },
-      "fields": [
-        {
-          "id": "firstName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "First Name",
-          "label": {
-            "eng": "First Name",
-            "por": "Primeiro nome"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "FullName",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "firstName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "surname",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Surname",
-          "label": {
-            "eng": "Surname",
-            "por": "Sobrenome"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "FullName",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "surname",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "dateOfBirth",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "dateOfBirth",
-          "label": {
-            "eng": "Date of Birth",
-            "por": "Data de nascimento"
-          },
-          "controlType": "ageDate",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "DateOfBirth",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "dateOfBirth",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "gender",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "gender",
-          "label": {
-            "eng": "Gender",
-            "por": "Gênero"
-          },
-          "controlType": "button",
-          "fieldType": "dynamic",
-          "format": "",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "group1",
-          "visible": null,
-          "contactType": null,
-          "group": "Gender",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "gender",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "height",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Height",
-          "label": {
-            "eng": "Height (cm)",
-            "por": "Altura (cm)"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^[0-9]{1,3}$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "PhysicalDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "height",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "residenceStatus",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "residenceStatus",
-          "label": {
-            "eng": "Residence Status",
-            "por": "Status de residência"
-          },
-          "controlType": "button",
-          "fieldType": "dynamic",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "kyc",
-          "alignmentGroup": "group1",
-          "visible": null,
-          "contactType": null,
-          "group": "ResidenceStatus",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "residenceStatus",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "countryOfCitizenship",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Country of Citizenship",
-          "label": {
-            "eng": "Country of Citizenship",
-            "por": "País de cidadania"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": null,
-          "group": "CountryOfCitizenship",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "countryOfCitizenship",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "maritalStatus",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Marital Status",
-          "label": {
-            "eng": "Marital Status",
-            "por": "Estado civil"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "MaritalStatus",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "maritalStatus",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "fatherName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Father's Name",
-          "label": {
-            "eng": "Father's Name",
-            "por": "Nome do pai"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "ParentsDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "fatherName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "motherName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Mother's Name",
-          "label": {
-            "eng": "Mother's Name",
-            "por": "Nome da mãe"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{2,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": null,
-          "visible": null,
-          "contactType": null,
-          "group": "ParentsDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "motherName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "addressLine1",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "addressLine1",
-          "label": {
-            "eng": "Address Line 1",
-            "por": "Endereço, linha 1"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{0,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "address",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Address",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "addressLine1",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "addressLine2",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "addressLine2",
-          "label": {
-            "eng": "Address Line 2",
-            "por": "Endereço, linha 2"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^(?=.{3,50}$).*",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "address",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Address",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "addressLine2",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "island",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Island",
-          "label": {
-            "eng": "Island",
-            "por": "Ilha"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Ilhas",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "district",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "District",
-          "label": {
-            "eng": "District",
-            "por": "Distrito"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Distrito",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "town",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Town",
-          "label": {
-            "eng": "Town",
-            "por": "Cidade"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Cidade",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "municipality",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Municipality",
-          "label": {
-            "eng": "Municipality",
-            "por": "Município"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "location",
-          "visible": null,
-          "contactType": "Postal",
-          "group": "Location",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Município",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "mobileNumber",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Mobile Number",
-          "label": {
-            "eng": "Mobile Number",
-            "por": "Número de celular"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^\\+239\\s?[0-9]{7}$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "contact",
-          "visible": null,
-          "contactType": "Phone",
-          "group": "Phone",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "MobileNumber",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "email",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "email",
-          "label": {
-            "eng": "Email",
-            "por": "E-mail"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "pvt",
-          "alignmentGroup": "contact",
-          "visible": null,
-          "contactType": "email",
-          "group": "Email",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [],
-          "subType": "Email",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "introducerName",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "introducerName",
-          "label": {
-            "eng": "Legal Guardian Name",
-            "por": "Nome do responsável legal"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "evidence",
-          "alignmentGroup": "introducer",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "identity.get('ageGroup') == 'INFANT'"
-          },
-          "contactType": null,
-          "group": "IntroducerDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "identity.get('ageGroup') == 'INFANT'"
-            }
-          ],
-          "subType": "introducerName",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "introducerRID",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "introducerRID",
-          "label": {
-            "eng": "Legal Guardian RID",
-            "por": "RID do responsável legal"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^([0-9]{10,30})$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "evidence",
-          "alignmentGroup": "introducer",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"
-          },
-          "contactType": null,
-          "group": "IntroducerDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"
-            }
-          ],
-          "subType": "RID",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "introducerUIN",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "introducerUIN",
-          "label": {
-            "eng": "Legal Guardian UIN",
-            "por": "UIN do responsável legal"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [
-            {
-              "type": "regex",
-              "validator": "^([0-9]{10,30})$",
-              "arguments": [],
-              "langCode": null,
-              "errorCode": null
-            }
-          ],
-          "fieldCategory": "evidence",
-          "alignmentGroup": "introducer",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"
-          },
-          "contactType": null,
-          "group": "IntroducerDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"
-            }
-          ],
-          "subType": "UIN",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "passportNumber",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Passport Number",
-          "label": {
-            "eng": "Passport Number",
-            "por": "Número do passaporte"
-          },
-          "controlType": "textbox",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "kyc",
-          "alignmentGroup": null,
-          "visible": {
-            "engine": "MVEL",
-            "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-          },
-          "contactType": null,
-          "group": "PassportDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-            }
-          ],
-          "subType": "passportNumber",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "passportIssuingCountry",
-          "inputRequired": true,
-          "type": "simpleType",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Passport Issuing Country",
-          "label": {
-            "eng": "Issuing Country",
-            "por": "País emissor"
-          },
-          "controlType": "dropdown",
-          "fieldType": "default",
-          "format": "none",
-          "validators": [],
-          "fieldCategory": "kyc",
-          "alignmentGroup": "location",
-          "visible": {
-            "engine": "MVEL",
-            "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-          },
-          "contactType": null,
-          "group": "PassportDetails",
-          "groupLabel": null,
-          "changeAction": null,
-          "transliterate": false,
-          "templateName": null,
-          "fieldLayout": null,
-          "locationHierarchy": null,
-          "conditionalBioAttributes": null,
-          "required": false,
-          "bioAttributes": null,
-          "requiredOn": [
-            {
-              "engine": "MVEL",
-              "expr": "!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"
-            }
-          ],
-          "subType": "passportIssuingCountry",
-          "exceptionPhotoRequired": false
-        },
-        {
-          "id": "passportDateOfIssue",
-          "inputRequired": true,
-          "type": "string",
-          "minimum": 0,
-          "maximum": 0,
-          "description": "Date of Issue",
-          "label": </t>
-  </si>
-  <si>
-    <t>{
-	"id": "BIOMETRIC_CORRECTION",
-	"order": 4,
-	"flow": "CORRECTION",
-	"isSubProcess": false,
-	"label": {
-		"por": "Correção biométrica",
-		"eng": "Biometric correction"
-	},
-	"screens": [
-		{
-			"order": 1,
-			"name": "consentdet",
-			"label": {
-				"por": "Consentimento",
-				"eng": "Consent"
-			},
-			"caption": {
-				"por": "Consentimento",
-				"eng": "Consent"
-			},
-			"fields": [
-				{
-					"id": "consentText",
-					"inputRequired": true,
-					"type": "simpleType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "Consent",
-					"label": {},
-					"controlType": "html",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consentText",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": "Registration Consent",
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consentText"
-				},
-				{
-					"id": "consent",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "consent accepted",
-					"label": {
-						"por": "Li e aceito os termos e condições para compartilhar minhas Personally Identifiable Information(PII)",
-						"eng": "I have read and accept terms and conditions to share my PII"
-					},
-					"controlType": "checkbox",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "consent",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "consent"
-				},
-				{
-					"id": "preferredLang",
-					"inputRequired": true,
-					"type": "string",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "user preferred Language",
-					"label": {
-						"por": "Idioma de notificação",
-						"eng": "Notification Langauge"
-					},
-					"controlType": "button",
-					"fieldType": "dynamic",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": "group1",
-					"visible": null,
-					"contactType": null,
-					"group": "PreferredLanguage",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": true,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "preferredLang"
-				}
-			],
-			"layoutTemplate": null,
-			"preRegFetchRequired": false,
-			"additionalInfoRequestIdRequired": false,
-			"active": false
-		},
-		{
-			"order": 3,
-			"name": "BiometricDetails",
-			"label": {
-				"por": "Detalhes biométricos",
-				"eng": "Biometric Details"
-			},
-			"caption": {
-				"por": "Detalhes biométricos",
-				"eng": "Biometric Details"
-			},
-			"fields": [
-				{
-					"id": "individualBiometrics",
-					"inputRequired": true,
-					"type": "biometricsType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "",
-					"label": {
-						"por": "Biometria do Candidato",
-						"eng": "Applicant Biometrics"
-					},
-					"controlType": "biometrics",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "pvt",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "Biometrics",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": [
-						{
-							"ageGroup": "INFANT",
-							"process": "ALL",
-							"validationExpr": "face",
-							"bioAttributes": [
-								"face"
-							]
-						}
-					],
-					"required": true,
-					"bioAttributes": [
-						"leftEye",
-						"rightEye",
-						"rightIndex",
-						"rightLittle",
-						"rightRing",
-						"rightMiddle",
-						"leftIndex",
-						"leftLittle",
-						"leftRing",
-						"leftMiddle",
-						"leftThumb",
-						"rightThumb",
-						"face"
-					],
-					"requiredOn": [],
-					"subType": "applicant"
-				},
-				{
-					"id": "proofOfException",
-					"inputRequired": false,
-					"type": "documentType",
-					"minimum": 0,
-					"maximum": 0,
-					"description": "proofOfException",
-					"label": {
-						"por": "Prova de exceção",
-						"eng": "Proof of Exception"
-					},
-					"controlType": "fileupload",
-					"fieldType": "default",
-					"format": "none",
-					"validators": [],
-					"fieldCategory": "evidence",
-					"alignmentGroup": null,
-					"visible": null,
-					"contactType": null,
-					"group": "Documents",
-					"groupLabel": null,
-					"changeAction": null,
-					"transliterate": false,
-					"templateName": null,
-					"fieldLayout": null,
-					"locationHierarchy": null,
-					"conditionalBioAttributes": null,
-					"required": false,
-					"bioAttributes": null,
-					"requiredOn": [],
-					"subType": "POE"
-				}
-			],
-			"layoutTemplate": null,
-			"preRegFetchRequired": false,
-			"active": false
-		}
-	],
-	"caption": {
-		"por": "Correção biométrica",
-		"eng": "Biometric correction"
-	},
-	"icon": "UINUpdate.png",
-	"isActive": true,
-	"autoSelectedGroups": null
-}</t>
   </si>
   <si>
     <t>[
@@ -4388,7 +1977,10 @@
 ]</t>
   </si>
   <si>
-    <t>{"id":"NEW","order":1,"flow":"NEW","label":{"por":"Novo registro","eng":"New Registration"},"screens":[{"order":1,"name":"consentdet","label":{"por":"Consentimento","eng":"Consent"},"caption":{"por":"Consentimento","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"por":"Li e aceito os termos e condições para compartilhar minhas informações pessoais.","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"por":"Idioma de notificação","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"por":"Detalhes demográficos","eng":"Demographic Details"},"caption":{"por":"Detalhes demográficos","eng":"Demographic Details"},"fields":[{"id":"firstName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"First Name","label":{"por":"Primeiro nome","eng":"First Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"firstName"},{"id":"surname","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Surname","label":{"por":"Sobrenome","eng":"Surname"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"surname"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"por":"Data de nascimento","eng":"Date of Birth"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"por":"Gênero","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"height","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Height","label":{"por":"Altura (cm)","eng":"Height (cm)"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[0-9]{1,3}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"PhysicalDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"height"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"por":"Status de residência","eng":"Residence Status"},"controlType":"dropdown","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"countryOfCitizenship","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Country of Citizenship","label":{"por":"País de cidadania","eng":"Country of Citizenship"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"CountryOfCitizenship","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"countryOfCitizenship"},{"id":"maritalStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Marital Status","label":{"por":"Estado civil","eng":"Marital Status"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"MaritalStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"maritalStatus"},{"id":"fatherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Father's Name","label":{"por":"Nome do pai","eng":"Father's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"fatherName"},{"id":"motherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Mother's Name","label":{"por":"Nome da mãe","eng":"Mother's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"motherName"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"por":"Endereço, linha 1","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"por":"Endereço, linha 2","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"island","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Island","label":{"por":"Ilha","eng":"Island"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Ilhas"},{"id":"district","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"District","label":{"por":"Distrito","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Distrito"},{"id":"town","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Town","label":{"por":"Cidade","eng":"Town"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Cidade"},{"id":"municipality","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Municipality","label":{"por":"Município","eng":"Municipality"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Município"},{"id":"mobileNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Mobile Number","label":{"por":"Número de celular","eng":"Mobile Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^\\+239\\s?[0-9]{7}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"Phone","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"MobileNumber"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"por":"E-mail","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"por":"Nome do responsável legal","eng":"Legal Guardian Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"por":"RID do responsável legal","eng":"Legal Guardian RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"por":"UIN do responsável legal","eng":"Legal Guardian UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"},{"id":"passportNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Passport Number","label":{"por":"Número do passaporte","eng":"Passport Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportNumber"},{"id":"passportIssuingCountry","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Passport Issuing Country","label":{"por":"País emissor","eng":"Issuing Country"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportIssuingCountry"},{"id":"passportDateOfIssue","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Issue","label":{"por":"Data de emissão","eng":"Date of Issue"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportDateOfIssue"},{"id":"passportDateOfExpiry","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Expiry","label":{"por":"Data de validade","eng":"Date of Expiry"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('residenceStatus')[0].value == 'Cidadão' || identity.get('residenceStatus')[1].value == 'Cidadão')"}],"subType":"passportDateOfExpiry"}],"layoutTemplate":null,"preRegFetchRequired":true,"additionalInfoRequestIdRequired":false,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","por":"Carregamento de documentos","fra":"Des documents","eng":"Document Upload"},"caption":{"por":"Documentos","eng":"Documents"},"fields":[{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"por":"Prova de identidade","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"por":"Prova de relacionamento","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"por":"Prova de data de nascimento","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"por":"Prova de exceção","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"por":"Detalhes biométricos","eng":"Biometric Details"},"caption":{"por":"Detalhes biométricos","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do candidato","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"exceptionPhotoRequired":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do Introdutor","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"exceptionPhotoRequired":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false}],"caption":{"por":"Novo registro","eng":"New Registration"},"icon":"NewReg.png","autoSelectedGroups":null,"active":true,"isActive":true}</t>
+    <t>{"id":"UPDATE","order":2,"flow":"UPDATE","label":{"por":"Atualizar UIN","eng":"Update UIN"},"screens":[{"order":1,"name":"consentdet","label":{"por":"Consentimento","eng":"Consent"},"caption":{"por":"Consentimento","eng":"Consent"},"fields":[{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Consent","groupLabel":{"por":"Consentimento","eng":"Consent"},"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"por":"Li e aceito os termos e condições para compartilhar minhas informações pessoais.","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Consent","groupLabel":{"por":"Consentimento","eng":"Consent"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"por":"Idioma de notificação","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":{"por":"Idioma de notificação","eng":"Notification Langauge"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"por":"Detalhes demográficos","eng":"Demographic Details"},"caption":{"por":"Detalhes demográficos","eng":"Demographic Details"},"fields":[{"id":"firstName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"First Name","label":{"por":"Primeiro nome","eng":"First Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":{"por":"Nome completo","eng":"Full Name"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"firstName"},{"id":"surname","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Surname","label":{"por":"Sobrenome","eng":"Surname"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":{"por":"Nome completo","eng":"Full Name"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"surname"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"por":"Data de nascimento","eng":"Date of Birth"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":{"por":"Data de nascimento","eng":"Date of Birth"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"por":"Gênero","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":{"por":"Gênero","eng":"Gender"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"height","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Height","label":{"por":"Altura (cm)","eng":"Height (cm)"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[0-9]{1,3}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"PhysicalDetails","groupLabel":{"por":"Detalhes físicos","eng":"Physical Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"height"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"por":"Status de residência","eng":"Residence Status"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":{"por":"Status de residência","eng":"Residence Status"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"placeOfBirth","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Place of Birth","label":{"por":"Local de Nascimento","eng":"Place of Birth"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') == 'CO'"},"contactType":null,"group":"PlaceOfBirth","groupLabel":{"por":"Local de Nascimento","eng":"Place of Birth"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') == 'CO'"}],"subType":"Distrito"},{"id":"countryOfCitizenship","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Country of Citizenship","label":{"por":"País de cidadania","eng":"Country of Citizenship"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":null,"group":"CountryOfCitizenship","groupLabel":{"por":"País de cidadania","eng":"Country of Citizenship"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"countryOfCitizenship"},{"id":"maritalStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Marital Status","label":{"por":"Estado civil","eng":"Marital Status"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"MaritalStatus","groupLabel":{"por":"Estado civil","eng":"Marital Status"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"maritalStatus"},{"id":"fatherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Father's Name","label":{"por":"Nome do pai","eng":"Father's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":{"por":"Detalhes dos pais","eng":"Parents Details"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"fatherName"},{"id":"motherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Mother's Name","label":{"por":"Nome da mãe","eng":"Mother's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":{"por":"Detalhes dos pais","eng":"Parents Details"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"motherName"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"por":"Endereço, linha 1","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":{"por":"Endereço","eng":"Address"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"por":"Endereço, linha 2","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":{"por":"Endereço","eng":"Address"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"island","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Island","label":{"por":"Ilha","eng":"Island"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":{"por":"Localização local","eng":"Local Location"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Ilhas"},{"id":"district","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"District","label":{"por":"Distrito","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":{"por":"Localização local","eng":"Local Location"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Distrito"},{"id":"town","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Town","label":{"por":"Cidade","eng":"Town"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":{"por":"Localização local","eng":"Local Location"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Cidade"},{"id":"municipality","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Municipality","label":{"por":"Município","eng":"Municipality"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"location","visible":null,"contactType":"Postal","group":"Location","groupLabel":{"por":"Localização local","eng":"Local Location"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Município"},{"id":"mobileNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Mobile Number","label":{"por":"Número de celular","eng":"Mobile Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^\\+239\\s?[0-9]{7}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"Phone","group":"Phone","groupLabel":{"por":"Telefone","eng":"Phone"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"MobileNumber"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"por":"E-mail","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":{"por":"E-mail","eng":"Email"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Legal Guardian Name","label":{"por":"Nome do responsável legal","eng":"Legal Guardian Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":null,"contactType":null,"group":"IntroducerDetails","groupLabel":{"por":"Detalhes do responsável legal","eng":"Legal Guardian Details"},"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Legal Guardian RID","label":{"por":"RID do responsável legal","eng":"Legal Guardian RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty"},"contactType":null,"group":"IntroducerDetails","groupLabel":{"por":"Detalhes do responsável legal","eng":"Legal Guardian Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Legal Guardian UIN","label":{"por":"UIN do responsável legal","eng":"Legal Guardian UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('introducerRID') == nil || identity.get('introducerRID') == empty"},"contactType":null,"group":"IntroducerDetails","groupLabel":{"por":"Detalhes do responsável legal","eng":"Legal Guardian Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('introducerRID') == nil || identity.get('introducerRID') == empty"}],"subType":"UIN"},{"id":"passportNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Passport Number","label":{"por":"Número do passaporte","eng":"Passport Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":{"por":"Detalhes do passaporte","eng":"Passport Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportNumber"},{"id":"passportIssuingCountry","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Passport Issuing Country","label":{"por":"País emissor","eng":"Issuing Country"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"location","visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":{"por":"Detalhes do passaporte","eng":"Passport Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportIssuingCountry"},{"id":"passportDateOfIssue","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Issue","label":{"por":"Data de emissão","eng":"Date of Issue"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":{"por":"Detalhes do passaporte","eng":"Passport Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportDateOfIssue"},{"id":"passportDateOfExpiry","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Expiry","label":{"por":"Data de validade","eng":"Date of Expiry"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":{"por":"Detalhes do passaporte","eng":"Passport Details"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportDateOfExpiry"}],"layoutTemplate":null,"preRegFetchRequired":true,"additionalInfoRequestIdRequired":false,"active":false},{"order":3,"name":"Documents","label":{"por":"Carregamento de documentos","eng":"Document Upload"},"caption":{"por":"Documentos","eng":"Documents"},"fields":[{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"por":"Prova de identidade","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":{"por":"Documentos","eng":"Documents"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.updatableFieldGroups contains 'FullName' || identity.updatableFieldGroups contains 'DateOfBirth'"}],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"por":"Prova de relacionamento","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":{"por":"Documentos","eng":"Documents"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' || identity.updatableFieldGroups contains 'IntroducerDetails'"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"por":"Prova de data de nascimento","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":{"por":"Documentos","eng":"Documents"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.updatableFieldGroups contains 'DateOfBirth'"}],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"por":"Prova de exceção","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":{"por":"Documentos","eng":"Documents"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"por":"Detalhes biométricos","eng":"Biometric Details"},"caption":{"por":"Detalhes biométricos","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do candidato","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":{"por":"Biométricos","eng":"Biometrics"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"exceptionPhotoRequired":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.updatableFieldGroups contains 'Biometrics'"}],"subType":"applicant"},{"id":"individualAuthBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"Used to hold biometrics only for authentication","label":{"por":"Autenticação biométrica","eng":"Authentication Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":{"por":"Biométricos","eng":"Biometrics"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"ALL","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"exceptionPhotoRequired":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"!(identity.get('ageGroup') == 'INFANT') &amp;&amp; !(identity.updatableFieldGroups contains 'Biometrics')"}],"subType":"applicant-auth"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria de Introdução","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":{"por":"Biométricos","eng":"Biometrics"},"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"ALL","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"exceptionPhotoRequired":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' || identity.updatableFieldGroups contains 'IntroducerDetails'"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false}],"caption":{"por":"Atualizar UIN","eng":"Update UIN"},"icon":"UINUpdate.png","autoSelectedGroups":["Consent","PreferredLanguage","Documents","Biometrics"],"active":true,"isActive":true}</t>
+  </si>
+  <si>
+    <t>{"id":"NEW","order":1,"flow":"NEW","label":{"por":"Novo registro","eng":"New Registration"},"screens":[{"order":1,"name":"consentdet","label":{"por":"Consentimento","eng":"Consent"},"caption":{"por":"Consentimento","eng":"Consent"},"fields":[{"id":"IDSchemaVersion","inputRequired":false,"type":"number","minimum":0,"maximum":0,"description":"ID Schema Version","label":{"eng":"IDSchemaVersion"},"controlType":null,"fieldType":"default","format":"none","validators":[],"fieldCategory":"none","alignmentGroup":null,"visible":null,"contactType":null,"group":null,"groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"IdSchemaVersion"},{"id":"consentText","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Consent","label":{},"controlType":"html","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consentText","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":"Registration Consent","fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consentText"},{"id":"consent","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"consent accepted","label":{"por":"Li e aceito os termos e condições para compartilhar minhas informações pessoais.","eng":"I have read and accept terms and conditions to share my PII"},"controlType":"checkbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"consent","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"consent"},{"id":"preferredLang","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"user preferred Language","label":{"por":"Idioma de notificação","eng":"Notification Langauge"},"controlType":"button","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"PreferredLanguage","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"preferredLang"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":2,"name":"DemographicDetails","label":{"por":"Detalhes demográficos","eng":"Demographic Details"},"caption":{"por":"Detalhes demográficos","eng":"Demographic Details"},"fields":[{"id":"firstName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"First Name","label":{"por":"Primeiro nome","eng":"First Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"firstName"},{"id":"surname","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Surname","label":{"por":"Sobrenome","eng":"Surname"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"FullName","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"surname"},{"id":"dateOfBirth","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"dateOfBirth","label":{"por":"Data de nascimento","eng":"Date of Birth"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"DateOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"dateOfBirth"},{"id":"gender","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"gender","label":{"por":"Gênero","eng":"Gender"},"controlType":"button","fieldType":"dynamic","format":"","validators":[],"fieldCategory":"pvt","alignmentGroup":"group1","visible":null,"contactType":null,"group":"Gender","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"gender"},{"id":"height","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Height","label":{"por":"Altura (cm)","eng":"Height (cm)"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[0-9]{1,3}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"PhysicalDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"height"},{"id":"residenceStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"residenceStatus","label":{"por":"Status de residência","eng":"Residence Status"},"controlType":"dropdown","fieldType":"dynamic","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":"group1","visible":null,"contactType":null,"group":"ResidenceStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"residenceStatus"},{"id":"placeOfBirth","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Place of Birth","label":{"por":"Local de Nascimento","eng":"Place of Birth"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') == 'CO'"},"contactType":null,"group":"PlaceOfBirth","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') == 'CO'"}],"subType":"Distrito"},{"id":"countryOfCitizenship","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Country of Citizenship","label":{"por":"País de cidadania","eng":"Country of Citizenship"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"CountryOfCitizenship","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"countryOfCitizenship"},{"id":"maritalStatus","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Marital Status","label":{"por":"Estado civil","eng":"Marital Status"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"MaritalStatus","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"maritalStatus"},{"id":"fatherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Father's Name","label":{"por":"Nome do pai","eng":"Father's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"fatherName"},{"id":"motherName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Mother's Name","label":{"por":"Nome da mãe","eng":"Mother's Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{2,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"ParentsDetails","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"motherName"},{"id":"addressLine1","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine1","label":{"por":"Endereço, linha 1","eng":"Address Line 1"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{0,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine1"},{"id":"addressLine2","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"addressLine2","label":{"por":"Endereço, linha 2","eng":"Address Line 2"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(?=.{3,50}$).*","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"address","visible":null,"contactType":"Postal","group":"Address","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"addressLine2"},{"id":"island","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Island","label":{"por":"Ilha","eng":"Island"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Ilhas"},{"id":"district","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"District","label":{"por":"Distrito","eng":"District"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Distrito"},{"id":"town","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Town","label":{"por":"Cidade","eng":"Town"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Cidade"},{"id":"municipality","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Municipality","label":{"por":"Município","eng":"Municipality"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":"LocationLocal","visible":null,"contactType":"Postal","group":"LocationLocal","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Município"},{"id":"mobileNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Mobile Number","label":{"por":"Número de celular","eng":"Mobile Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^\\+?[1-9][0-9]{7,14}$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"Phone","group":"Phone","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"MobileNumber"},{"id":"email","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"email","label":{"por":"E-mail","eng":"Email"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^[A-Za-z0-9_\\-]+(\\.[A-Za-z0-9_]+)*@[A-Za-z0-9_-]+(\\.[A-Za-z0-9_]+)*(\\.[a-zA-Z]{2,})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"pvt","alignmentGroup":"contact","visible":null,"contactType":"email","group":"Email","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"Email"},{"id":"introducerName","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"introducerName","label":{"por":"Nome do responsável legal","eng":"Legal Guardian Name"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR'"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":true,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"( identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR' )"}],"subType":"introducerName"},{"id":"introducerRID","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerRID","label":{"por":"RID do responsável legal","eng":"Legal Guardian RID"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"(identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR') &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"(identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR') &amp;&amp; (identity.get('introducerUIN') == nil || identity.get('introducerUIN') == empty)"}],"subType":"RID"},{"id":"introducerUIN","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"introducerUIN","label":{"por":"UIN do responsável legal","eng":"Legal Guardian UIN"},"controlType":"textbox","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^([0-9]{10,30})$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"evidence","alignmentGroup":"introducer","visible":{"engine":"MVEL","expr":"(identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR') &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"},"contactType":null,"group":"IntroducerDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"(identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR') &amp;&amp; (identity.get('introducerRID') == nil || identity.get('introducerRID') == empty)"}],"subType":"UIN"},{"id":"passportNumber","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Passport Number","label":{"por":"Número do passaporte","eng":"Passport Number"},"controlType":"textbox","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportNumber"},{"id":"passportIssuingCountry","inputRequired":true,"type":"simpleType","minimum":0,"maximum":0,"description":"Passport Issuing Country","label":{"por":"País emissor","eng":"Issuing Country"},"controlType":"dropdown","fieldType":"default","format":"none","validators":[],"fieldCategory":"kyc","alignmentGroup":null,"visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportIssuingCountry"},{"id":"passportDateOfIssue","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Issue","label":{"por":"Data de emissão","eng":"Date of Issue"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportDateOfIssue"},{"id":"passportDateOfExpiry","inputRequired":true,"type":"string","minimum":0,"maximum":0,"description":"Date of Expiry","label":{"por":"Data de validade","eng":"Date of Expiry"},"controlType":"ageDate","fieldType":"default","format":"none","validators":[{"type":"regex","validator":"^(1869|18[7-9][0-9]|19[0-9][0-9]|20[0-9][0-9])/([0][1-9]|1[0-2])/([0][1-9]|[1-2][0-9]|3[01])$","arguments":[],"langCode":null,"errorCode":null}],"fieldCategory":"kyc","alignmentGroup":"PassportDetails","visible":{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"},"contactType":null,"group":"PassportDetails","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('residenceStatusCode') != null &amp;&amp; identity.get('residenceStatusCode') != 'CO'"}],"subType":"passportDateOfExpiry"}],"layoutTemplate":null,"preRegFetchRequired":true,"additionalInfoRequestIdRequired":false,"active":false},{"order":3,"name":"Documents","label":{"ara":"تحميل الوثيقة","por":"Carregamento de documentos","fra":"Des documents","eng":"Document Upload"},"caption":{"por":"Documentos","eng":"Documents"},"fields":[{"id":"proofOfIdentity","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfIdentity","label":{"por":"Prova de identidade","eng":"Identity Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":true,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POI"},{"id":"proofOfRelationship","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfRelationship","label":{"por":"Prova de relacionamento","eng":"Relationship Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"( identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR')"}],"subType":"POR"},{"id":"proofOfDateOfBirth","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfDateOfBirth","label":{"por":"Prova de data de nascimento","eng":"DOB Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[{"engine":"MVEL","expr":"identity.get('ageGroup') == 'INFANT'"}],"subType":"POB"},{"id":"proofOfException","inputRequired":true,"type":"documentType","minimum":0,"maximum":0,"description":"proofOfException","label":{"por":"Prova de exceção","eng":"Exception Proof"},"controlType":"fileupload","fieldType":"default","format":"none","validators":[],"fieldCategory":"evidence","alignmentGroup":null,"visible":null,"contactType":null,"group":"Documents","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":null,"required":false,"exceptionPhotoRequired":false,"bioAttributes":null,"requiredOn":[],"subType":"POE"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false},{"order":4,"name":"BiometricDetails","label":{"por":"Detalhes biométricos","eng":"Biometric Details"},"caption":{"por":"Detalhes biométricos","eng":"Biometric Details"},"fields":[{"id":"individualBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do candidato","eng":"Applicant Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"face","bioAttributes":["face"]}],"required":true,"exceptionPhotoRequired":true,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[],"subType":"applicant"},{"id":"introducerBiometrics","inputRequired":true,"type":"biometricsType","minimum":0,"maximum":0,"description":"","label":{"por":"Biometria do Introdutor","eng":"Introducer Biometrics"},"controlType":"biometrics","fieldType":"default","format":"none","validators":[],"fieldCategory":"pvt","alignmentGroup":null,"visible":null,"contactType":null,"group":"Biometrics","groupLabel":null,"changeAction":null,"transliterate":false,"templateName":null,"fieldLayout":null,"locationHierarchy":null,"conditionalBioAttributes":[{"ageGroup":"INFANT","process":"ALL","validationExpr":"leftEye || rightEye || rightIndex || rightLittle || rightRing || rightMiddle || leftIndex || leftLittle || leftRing || leftMiddle || leftThumb || rightThumb || face","bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"]}],"required":false,"exceptionPhotoRequired":false,"bioAttributes":["leftEye","rightEye","rightIndex","rightLittle","rightRing","rightMiddle","leftIndex","leftLittle","leftRing","leftMiddle","leftThumb","rightThumb","face"],"requiredOn":[{"engine":"MVEL","expr":"(identity.get('ageGroup') == 'INFANT' || identity.get('ageGroup') == 'MINOR')"}],"subType":"introducer"}],"layoutTemplate":null,"preRegFetchRequired":false,"additionalInfoRequestIdRequired":false,"active":false}],"caption":{"por":"Novo registro","eng":"New Registration"},"icon":"NewReg.png","autoSelectedGroups":null,"active":true,"isActive":true}</t>
   </si>
 </sst>
 </file>
@@ -4785,7 +2377,7 @@
         <v>28</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H2" s="6">
         <v>1001</v>
@@ -4839,7 +2431,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H3" s="6">
         <v>1001</v>
@@ -4893,7 +2485,7 @@
         <v>31</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="H4" s="6">
         <v>1001</v>
@@ -4929,7 +2521,7 @@
     </row>
     <row r="5" spans="1:26" ht="30.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" s="6">
         <v>0.1</v>
@@ -4938,16 +2530,16 @@
         <v>18</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H5" s="6">
         <v>1001</v>
@@ -4965,13 +2557,13 @@
         <v>22</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>20</v>
@@ -4983,7 +2575,7 @@
     </row>
     <row r="6" spans="1:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" s="6">
         <v>0.1</v>
@@ -4992,16 +2584,16 @@
         <v>25</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>34</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H6" s="6">
         <v>1001</v>
@@ -5045,7 +2637,7 @@
     </row>
     <row r="7" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="6">
         <v>0.1</v>
@@ -5054,16 +2646,16 @@
         <v>25</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H7" s="6">
         <v>1001</v>
@@ -5106,57 +2698,23 @@
       <c r="Z7" s="4"/>
     </row>
     <row r="8" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B8" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="6">
-        <v>1001</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="6">
-        <v>110024</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O8" s="6">
-        <v>110024</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q8" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
@@ -5168,57 +2726,23 @@
       <c r="Z8" s="4"/>
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="6">
-        <v>1001</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="6">
-        <v>110024</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="O9" s="6">
-        <v>110024</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q9" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="6"/>
       <c r="R9" s="6"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
